--- a/docs/reports/HCC.xlsx
+++ b/docs/reports/HCC.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>104.2292086294086</v>
+        <v>104.2285447304735</v>
       </c>
     </row>
     <row r="8">
@@ -3215,13 +3215,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>114.8694451681721</v>
+        <v>114.867390862262</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>96.6855709907631</v>
+        <v>96.68388820440332</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>135.6936947636777</v>
+        <v>135.6911871701842</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0.3</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>0.08650531009399476</v>
+        <v>0.08650414209792812</v>
       </c>
     </row>
     <row r="13">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>93.92</v>
+        <v>94.02</v>
       </c>
     </row>
     <row r="19">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>104.2292086294086</v>
+        <v>104.2285447304735</v>
       </c>
     </row>
     <row r="21">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>93.92</v>
+        <v>94.02</v>
       </c>
     </row>
     <row r="6">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>0.06946519397344908</v>
+        <v>0.06946614402227673</v>
       </c>
       <c r="B5" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5667,7 +5667,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>0.07696519397344909</v>
+        <v>0.07696614402227672</v>
       </c>
       <c r="B6" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>0.08446519397344908</v>
+        <v>0.08446614402227673</v>
       </c>
       <c r="B7" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>0.09196519397344907</v>
+        <v>0.09196614402227674</v>
       </c>
       <c r="B8" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
@@ -5742,7 +5742,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>0.09946519397344908</v>
+        <v>0.09946614402227673</v>
       </c>
       <c r="B9" s="16">
         <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
